--- a/tables/new/balanced all/all_Disc_Cum_Gain.xlsx
+++ b/tables/new/balanced all/all_Disc_Cum_Gain.xlsx
@@ -425,36 +425,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Logit(1, 1, 1, 1)_ABROOD</t>
+          <t>XGBoost(1, 1, 1, 1)_ABROOD</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>XGBoost(1, 1, 1, 1)_ABROOD</t>
+          <t>Logit(1, 1, 0, 0)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Logit(1, 1, 0, 0)</t>
+          <t>XGBoost(1, 1, 0, 0)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>XGBoost(1, 1, 0, 0)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Logit(1, 1, 1, 1)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>XGBoost(1, 1, 1, 1)</t>
         </is>
@@ -467,21 +457,15 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13.53496712564771</v>
+        <v>14.8126183987172</v>
       </c>
       <c r="C2" t="n">
-        <v>14.8126183987172</v>
+        <v>14.20920706663408</v>
       </c>
       <c r="D2" t="n">
-        <v>14.20920706663408</v>
+        <v>14.67367261431595</v>
       </c>
       <c r="E2" t="n">
-        <v>14.67367261431595</v>
-      </c>
-      <c r="F2" t="n">
-        <v>13.71382286094049</v>
-      </c>
-      <c r="G2" t="n">
         <v>14.86557288352323</v>
       </c>
     </row>
@@ -492,21 +476,15 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.377592170846322</v>
+        <v>3.566065781122415</v>
       </c>
       <c r="C3" t="n">
-        <v>3.566065781122415</v>
+        <v>3.510510892347474</v>
       </c>
       <c r="D3" t="n">
-        <v>3.510510892347474</v>
+        <v>3.136999015261328</v>
       </c>
       <c r="E3" t="n">
-        <v>3.136999015261328</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3.610016712454063</v>
-      </c>
-      <c r="G3" t="n">
         <v>3.217941060456761</v>
       </c>
     </row>
@@ -517,21 +495,15 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.11529205920556</v>
+        <v>13.02542272084979</v>
       </c>
       <c r="C4" t="n">
-        <v>13.02542272084979</v>
+        <v>12.93854108129046</v>
       </c>
       <c r="D4" t="n">
-        <v>12.93854108129046</v>
+        <v>12.8944923645084</v>
       </c>
       <c r="E4" t="n">
-        <v>12.8944923645084</v>
-      </c>
-      <c r="F4" t="n">
-        <v>13.11508753741141</v>
-      </c>
-      <c r="G4" t="n">
         <v>12.98260606109335</v>
       </c>
     </row>
@@ -542,21 +514,15 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.612381074199089</v>
+        <v>9.245506281043133</v>
       </c>
       <c r="C5" t="n">
-        <v>9.245506281043133</v>
+        <v>8.636900093613765</v>
       </c>
       <c r="D5" t="n">
-        <v>8.636900093613765</v>
+        <v>9.379285032438901</v>
       </c>
       <c r="E5" t="n">
-        <v>9.379285032438901</v>
-      </c>
-      <c r="F5" t="n">
-        <v>8.395308661995324</v>
-      </c>
-      <c r="G5" t="n">
         <v>9.283228476520009</v>
       </c>
     </row>
@@ -567,21 +533,15 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.08178116656023</v>
+        <v>15.31397803654155</v>
       </c>
       <c r="C6" t="n">
-        <v>15.31397803654155</v>
+        <v>15.23078662840116</v>
       </c>
       <c r="D6" t="n">
-        <v>15.23078662840116</v>
+        <v>15.39754419139637</v>
       </c>
       <c r="E6" t="n">
-        <v>15.39754419139637</v>
-      </c>
-      <c r="F6" t="n">
-        <v>15.23448395494262</v>
-      </c>
-      <c r="G6" t="n">
         <v>15.27718688434119</v>
       </c>
     </row>
@@ -592,21 +552,15 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.15686695764686</v>
+        <v>4.503808814147737</v>
       </c>
       <c r="C7" t="n">
-        <v>4.503808814147737</v>
+        <v>4.086962538287968</v>
       </c>
       <c r="D7" t="n">
-        <v>4.086962538287968</v>
+        <v>4.408055662514128</v>
       </c>
       <c r="E7" t="n">
-        <v>4.408055662514128</v>
-      </c>
-      <c r="F7" t="n">
-        <v>4.169583005394124</v>
-      </c>
-      <c r="G7" t="n">
         <v>4.52902616950604</v>
       </c>
     </row>
@@ -617,21 +571,15 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.2189098077809</v>
+        <v>10.56500324767848</v>
       </c>
       <c r="C8" t="n">
-        <v>10.56500324767848</v>
+        <v>10.35301671078971</v>
       </c>
       <c r="D8" t="n">
-        <v>10.35301671078971</v>
+        <v>10.55196206488791</v>
       </c>
       <c r="E8" t="n">
-        <v>10.55196206488791</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10.33431508248938</v>
-      </c>
-      <c r="G8" t="n">
         <v>10.4223759665015</v>
       </c>
     </row>
@@ -642,21 +590,15 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.804505343265966</v>
+        <v>8.01465416590392</v>
       </c>
       <c r="C9" t="n">
-        <v>8.01465416590392</v>
+        <v>7.719191291288632</v>
       </c>
       <c r="D9" t="n">
-        <v>7.719191291288632</v>
+        <v>7.51694010639145</v>
       </c>
       <c r="E9" t="n">
-        <v>7.51694010639145</v>
-      </c>
-      <c r="F9" t="n">
-        <v>7.673989360381053</v>
-      </c>
-      <c r="G9" t="n">
         <v>7.837032226934334</v>
       </c>
     </row>
@@ -667,21 +609,15 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.388748191308444</v>
+        <v>6.13288600679655</v>
       </c>
       <c r="C10" t="n">
-        <v>6.13288600679655</v>
+        <v>5.298748137963479</v>
       </c>
       <c r="D10" t="n">
-        <v>5.298748137963479</v>
+        <v>5.458116240245714</v>
       </c>
       <c r="E10" t="n">
-        <v>5.458116240245714</v>
-      </c>
-      <c r="F10" t="n">
-        <v>5.65008258564089</v>
-      </c>
-      <c r="G10" t="n">
         <v>6.061640512139698</v>
       </c>
     </row>
@@ -692,21 +628,15 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7.887186888441627</v>
+        <v>8.994932264345985</v>
       </c>
       <c r="C11" t="n">
-        <v>8.994932264345985</v>
+        <v>7.942791263971387</v>
       </c>
       <c r="D11" t="n">
-        <v>7.942791263971387</v>
+        <v>8.787109166152792</v>
       </c>
       <c r="E11" t="n">
-        <v>8.787109166152792</v>
-      </c>
-      <c r="F11" t="n">
-        <v>7.784762087946158</v>
-      </c>
-      <c r="G11" t="n">
         <v>8.738239155982392</v>
       </c>
     </row>
@@ -717,21 +647,15 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.454797983361836</v>
+        <v>4.3364758458321</v>
       </c>
       <c r="C12" t="n">
-        <v>4.3364758458321</v>
+        <v>4.487088432064313</v>
       </c>
       <c r="D12" t="n">
-        <v>4.487088432064313</v>
+        <v>3.823100288159853</v>
       </c>
       <c r="E12" t="n">
-        <v>3.823100288159853</v>
-      </c>
-      <c r="F12" t="n">
-        <v>4.548543297938668</v>
-      </c>
-      <c r="G12" t="n">
         <v>4.046235648856241</v>
       </c>
     </row>
@@ -742,21 +666,15 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30.18402621886641</v>
+        <v>40.39412656101923</v>
       </c>
       <c r="C13" t="n">
-        <v>40.39412656101923</v>
+        <v>29.44891324927871</v>
       </c>
       <c r="D13" t="n">
-        <v>29.44891324927871</v>
+        <v>40.60749774478001</v>
       </c>
       <c r="E13" t="n">
-        <v>40.60749774478001</v>
-      </c>
-      <c r="F13" t="n">
-        <v>30.2882225532741</v>
-      </c>
-      <c r="G13" t="n">
         <v>40.01089939310785</v>
       </c>
     </row>
@@ -767,21 +685,15 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18.13442245504261</v>
+        <v>18.04086104170126</v>
       </c>
       <c r="C14" t="n">
-        <v>18.04086104170126</v>
+        <v>18.24845655149738</v>
       </c>
       <c r="D14" t="n">
-        <v>18.24845655149738</v>
+        <v>18.2387753498216</v>
       </c>
       <c r="E14" t="n">
-        <v>18.2387753498216</v>
-      </c>
-      <c r="F14" t="n">
-        <v>18.17436607642035</v>
-      </c>
-      <c r="G14" t="n">
         <v>18.06988259260727</v>
       </c>
     </row>
@@ -792,21 +704,15 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.58620093777248</v>
+        <v>7.429221292354683</v>
       </c>
       <c r="C15" t="n">
-        <v>7.429221292354683</v>
+        <v>6.496046860025015</v>
       </c>
       <c r="D15" t="n">
-        <v>6.496046860025015</v>
+        <v>7.228407567387654</v>
       </c>
       <c r="E15" t="n">
-        <v>7.228407567387654</v>
-      </c>
-      <c r="F15" t="n">
-        <v>6.941538110427762</v>
-      </c>
-      <c r="G15" t="n">
         <v>7.607110276976621</v>
       </c>
     </row>
@@ -817,21 +723,15 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11.11326895113763</v>
+        <v>12.05980439932908</v>
       </c>
       <c r="C16" t="n">
-        <v>12.05980439932908</v>
+        <v>12.07060926400992</v>
       </c>
       <c r="D16" t="n">
-        <v>12.07060926400992</v>
+        <v>12.25585970864144</v>
       </c>
       <c r="E16" t="n">
-        <v>12.25585970864144</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10.78852660200818</v>
-      </c>
-      <c r="G16" t="n">
         <v>12.23670884663189</v>
       </c>
     </row>
